--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P2">
         <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R2">
         <v>1.91</v>
@@ -653,10 +653,10 @@
         <v>1.59</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
         <v>1.2</v>
@@ -665,25 +665,25 @@
         <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y2">
         <v>1.52</v>
       </c>
       <c r="Z2">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AA2">
         <v>2.56</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC2">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AD2">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -708,7 +708,7 @@
         <v>1.61</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>1.48</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
         <v>6.5</v>
@@ -819,22 +819,22 @@
         <v>2.33</v>
       </c>
       <c r="U3">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z3">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AA3">
         <v>2.35</v>
@@ -852,10 +852,10 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -653,7 +653,7 @@
         <v>1.59</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
         <v>3.2</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -653,7 +653,7 @@
         <v>1.59</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
         <v>3.2</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -647,7 +647,7 @@
         <v>4.4</v>
       </c>
       <c r="R2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S2">
         <v>1.59</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:00</t>
+          <t>2026-09-22 13:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -647,7 +647,7 @@
         <v>4.4</v>
       </c>
       <c r="R2">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>1.59</v>
@@ -828,7 +828,7 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.44</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -686,7 +686,7 @@
         <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
         <v>2.15</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -849,13 +849,13 @@
         <v>1.11</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>2.5</v>
       </c>
       <c r="AG3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
         <v>2.75</v>
       </c>
       <c r="P2">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -650,49 +650,49 @@
         <v>1.95</v>
       </c>
       <c r="S2">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U2">
         <v>3.2</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
         <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y2">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="Z2">
         <v>2.4</v>
       </c>
       <c r="AA2">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="AB2">
         <v>1.4</v>
       </c>
       <c r="AC2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD2">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AE2">
         <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AG2">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
         <v>1.28</v>
@@ -828,7 +828,7 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
         <v>1.44</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,169 @@
       <c r="AU3" t="inlineStr">
         <is>
           <t>2026-09-22 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>3.14</v>
+      </c>
+      <c r="P4">
+        <v>4.1</v>
+      </c>
+      <c r="Q4">
+        <v>2.59</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>1.49</v>
+      </c>
+      <c r="T4">
+        <v>2.61</v>
+      </c>
+      <c r="U4">
+        <v>3.1</v>
+      </c>
+      <c r="V4">
+        <v>1.33</v>
+      </c>
+      <c r="W4">
+        <v>1.04</v>
+      </c>
+      <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.38</v>
+      </c>
+      <c r="Z4">
+        <v>2.62</v>
+      </c>
+      <c r="AA4">
+        <v>2.38</v>
+      </c>
+      <c r="AB4">
+        <v>1.58</v>
+      </c>
+      <c r="AC4">
+        <v>4.1</v>
+      </c>
+      <c r="AD4">
+        <v>1.16</v>
+      </c>
+      <c r="AE4">
+        <v>1.06</v>
+      </c>
+      <c r="AF4">
+        <v>2.05</v>
+      </c>
+      <c r="AG4">
+        <v>1.69</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.31</v>
+      </c>
+      <c r="AK4">
+        <v>1.78</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-1</v>
+      </c>
+      <c r="AN4">
+        <v>-1</v>
+      </c>
+      <c r="AO4">
+        <v>-1</v>
+      </c>
+      <c r="AP4">
+        <v>-1</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2026-09-22 19:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O4">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="P4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q4">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>1.49</v>
       </c>
       <c r="T4">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="U4">
         <v>3.1</v>
@@ -988,7 +988,7 @@
         <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.04</v>
@@ -1003,7 +1003,7 @@
         <v>2.38</v>
       </c>
       <c r="AB4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
         <v>4.1</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -638,25 +638,25 @@
         <v>2.5</v>
       </c>
       <c r="O2">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="P2">
         <v>2.75</v>
       </c>
       <c r="Q2">
-        <v>4.4</v>
+        <v>3.33</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="S2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T2">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="V2">
         <v>1.19</v>
@@ -665,7 +665,7 @@
         <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y2">
         <v>1.61</v>
@@ -674,25 +674,25 @@
         <v>2.4</v>
       </c>
       <c r="AA2">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AB2">
         <v>1.4</v>
       </c>
       <c r="AC2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD2">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AG2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
         <v>1.44</v>
@@ -852,7 +852,7 @@
         <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG3">
         <v>1.48</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="O4">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="Q4">
         <v>2.6</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="O4">
         <v>3.25</v>
       </c>
       <c r="P4">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T4">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="U4">
         <v>3.1</v>
@@ -991,34 +991,34 @@
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AA4">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK4">
         <v>1.78</v>

--- a/jogos_2026-09-22.xlsx
+++ b/jogos_2026-09-22.xlsx
@@ -631,68 +631,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="P2">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="R2">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="S2">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
         <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y2">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="Z2">
         <v>2.4</v>
       </c>
       <c r="AA2">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB2">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AC2">
         <v>5</v>
       </c>
       <c r="AD2">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.21</v>
+        <v>2.79</v>
       </c>
       <c r="AG2">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3">
@@ -804,7 +804,7 @@
         <v>3.3</v>
       </c>
       <c r="P3">
-        <v>6.5</v>
+        <v>5.82</v>
       </c>
       <c r="Q3">
         <v>2.18</v>
@@ -828,7 +828,7 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.44</v>
@@ -849,10 +849,10 @@
         <v>1.11</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG3">
         <v>1.48</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q4">
         <v>2.4</v>
@@ -979,7 +979,7 @@
         <v>1.5</v>
       </c>
       <c r="T4">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="U4">
         <v>3.1</v>
@@ -994,31 +994,31 @@
         <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z4">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA4">
         <v>2.45</v>
       </c>
       <c r="AB4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AC4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD4">
         <v>1.15</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AK4">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL4">
         <v>0</v>
